--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3071DDC7-C770-4618-AC83-02514DEFBF32}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37B0D421-593E-4450-A04D-6CBEA94608CA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,15 @@
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -26,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -197,6 +206,15 @@
   </si>
   <si>
     <t>Felt a bit tired today due to getting less sleep than usual.</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>today ws a geneuinely nice day.</t>
   </si>
 </sst>
 </file>
@@ -477,6 +495,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1022,26 +1044,50 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B7" s="14">
+        <v>480</v>
+      </c>
+      <c r="C7" s="14">
+        <v>60</v>
+      </c>
+      <c r="D7" s="14">
+        <v>150</v>
+      </c>
+      <c r="E7" s="14">
+        <v>60</v>
+      </c>
+      <c r="F7" s="14">
+        <v>300</v>
+      </c>
+      <c r="G7" s="14">
+        <v>6</v>
+      </c>
+      <c r="H7" s="14">
+        <v>120</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37B0D421-593E-4450-A04D-6CBEA94608CA}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D53A0024-70E7-4F34-9821-341EA99C92AF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -215,6 +215,9 @@
   </si>
   <si>
     <t>today ws a geneuinely nice day.</t>
+  </si>
+  <si>
+    <t>nice day.</t>
   </si>
 </sst>
 </file>
@@ -495,10 +498,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1090,26 +1089,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B8" s="14">
+        <v>420</v>
+      </c>
+      <c r="C8" s="14">
+        <v>60</v>
+      </c>
+      <c r="D8" s="14">
+        <v>125</v>
+      </c>
+      <c r="E8" s="14">
+        <v>90</v>
+      </c>
+      <c r="F8" s="14">
+        <v>300</v>
+      </c>
+      <c r="G8" s="14">
+        <v>6</v>
+      </c>
+      <c r="H8" s="14">
+        <v>140</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1135</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>305</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D53A0024-70E7-4F34-9821-341EA99C92AF}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4517C45B-3F67-4E12-8BE6-AB5F4B143D55}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -218,6 +218,9 @@
   </si>
   <si>
     <t>nice day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It was a nice day and I had my first mentor meeting at lpu. It was a great experience. </t>
   </si>
 </sst>
 </file>
@@ -498,6 +501,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1134,27 +1141,51 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+    <row r="9" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B9" s="14">
+        <v>540</v>
+      </c>
+      <c r="C9" s="14">
+        <v>60</v>
+      </c>
+      <c r="D9" s="14">
+        <v>90</v>
+      </c>
+      <c r="E9" s="14">
+        <v>40</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>150</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4517C45B-3F67-4E12-8BE6-AB5F4B143D55}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FA5C198-37AA-48A1-A7B7-DC29D9FFF397}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t xml:space="preserve">It was a nice day and I had my first mentor meeting at lpu. It was a great experience. </t>
+  </si>
+  <si>
+    <t>learning coding.</t>
   </si>
 </sst>
 </file>
@@ -1188,26 +1191,50 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B10" s="14">
+        <v>480</v>
+      </c>
+      <c r="C10" s="14">
+        <v>60</v>
+      </c>
+      <c r="D10" s="14">
+        <v>90</v>
+      </c>
+      <c r="E10" s="14">
+        <v>50</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>230</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FA5C198-37AA-48A1-A7B7-DC29D9FFF397}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D28C003-DE05-4AFB-9431-1628CB605960}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>learning coding.</t>
+  </si>
+  <si>
+    <t>great day.</t>
   </si>
 </sst>
 </file>
@@ -1237,26 +1240,50 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B11" s="14">
+        <v>480</v>
+      </c>
+      <c r="C11" s="14">
+        <v>60</v>
+      </c>
+      <c r="D11" s="14">
+        <v>120</v>
+      </c>
+      <c r="E11" s="14">
+        <v>70</v>
+      </c>
+      <c r="F11" s="14">
+        <v>150</v>
+      </c>
+      <c r="G11" s="14">
+        <v>3</v>
+      </c>
+      <c r="H11" s="14">
+        <v>240</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/CAP-776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D28C003-DE05-4AFB-9431-1628CB605960}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02EC043D-67F3-41CA-B129-D9FB52E4F6E2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -507,10 +507,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1241,7 +1237,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="13">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B11" s="14">
         <v>480</v>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/CAP-776/CAP-776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02EC043D-67F3-41CA-B129-D9FB52E4F6E2}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E44F334-B496-416A-BC3B-ECD320A3B176}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>great day.</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -507,6 +510,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1282,26 +1289,50 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B12" s="14">
+        <v>480</v>
+      </c>
+      <c r="C12" s="14">
+        <v>60</v>
+      </c>
+      <c r="D12" s="14">
+        <v>60</v>
+      </c>
+      <c r="E12" s="14">
+        <v>45</v>
+      </c>
+      <c r="F12" s="14">
+        <v>350</v>
+      </c>
+      <c r="G12" s="14">
+        <v>7</v>
+      </c>
+      <c r="H12" s="14">
+        <v>145</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E44F334-B496-416A-BC3B-ECD320A3B176}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9510048B-BED3-47E8-A0E7-9A04142E8B4C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
   </si>
 </sst>
 </file>
@@ -1335,26 +1338,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B13" s="14">
+        <v>480</v>
+      </c>
+      <c r="C13" s="14">
+        <v>60</v>
+      </c>
+      <c r="D13" s="14">
+        <v>30</v>
+      </c>
+      <c r="E13" s="14">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14">
+        <v>200</v>
+      </c>
+      <c r="G13" s="14">
+        <v>4</v>
+      </c>
+      <c r="H13" s="14">
+        <v>150</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>520</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9510048B-BED3-47E8-A0E7-9A04142E8B4C}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1C66EEA-88EF-43D5-A068-CD2DE43363B0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,9 @@
   </si>
   <si>
     <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>learning sothing new.</t>
   </si>
 </sst>
 </file>
@@ -1384,26 +1387,50 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B14" s="14">
+        <v>480</v>
+      </c>
+      <c r="C14" s="14">
+        <v>60</v>
+      </c>
+      <c r="D14" s="14">
+        <v>90</v>
+      </c>
+      <c r="E14" s="14">
+        <v>30</v>
+      </c>
+      <c r="F14" s="14">
+        <v>350</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="14">
+        <v>120</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="118" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1C66EEA-88EF-43D5-A068-CD2DE43363B0}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B5FED4C-3053-4971-9B4D-F5562B7235B2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>learning sothing new.</t>
+  </si>
+  <si>
+    <t>Excellent</t>
   </si>
 </sst>
 </file>
@@ -1433,26 +1436,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B15" s="14">
+        <v>480</v>
+      </c>
+      <c r="C15" s="14">
+        <v>60</v>
+      </c>
+      <c r="D15" s="14">
+        <v>90</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
+        <v>100</v>
+      </c>
+      <c r="G15" s="14">
+        <v>2</v>
+      </c>
+      <c r="H15" s="14">
+        <v>170</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="130" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B5FED4C-3053-4971-9B4D-F5562B7235B2}"/>
+  <xr:revisionPtr revIDLastSave="142" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2381D25-21DD-45EA-A52E-C0125C4ED0A7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -239,6 +239,12 @@
   </si>
   <si>
     <t>Excellent</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Bad Day.</t>
   </si>
 </sst>
 </file>
@@ -1482,26 +1488,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B16" s="14">
+        <v>420</v>
+      </c>
+      <c r="C16" s="14">
+        <v>60</v>
+      </c>
+      <c r="D16" s="14">
+        <v>60</v>
+      </c>
+      <c r="E16" s="14">
+        <v>40</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>125</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>705</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>735</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="142" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2381D25-21DD-45EA-A52E-C0125C4ED0A7}"/>
+  <xr:revisionPtr revIDLastSave="154" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDE88F1A-D22D-4577-A92F-946C64169F00}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1534,26 +1534,50 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B17" s="14">
+        <v>480</v>
+      </c>
+      <c r="C17" s="14">
+        <v>60</v>
+      </c>
+      <c r="D17" s="14">
+        <v>120</v>
+      </c>
+      <c r="E17" s="14">
+        <v>45</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>220</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>925</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>515</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="154" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDE88F1A-D22D-4577-A92F-946C64169F00}"/>
+  <xr:revisionPtr revIDLastSave="166" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57E45770-7208-4ED9-A073-DDE4E51A6262}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1580,26 +1580,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B18" s="14">
+        <v>480</v>
+      </c>
+      <c r="C18" s="14">
+        <v>60</v>
+      </c>
+      <c r="D18" s="14">
+        <v>145</v>
+      </c>
+      <c r="E18" s="14">
+        <v>30</v>
+      </c>
+      <c r="F18" s="14">
+        <v>100</v>
+      </c>
+      <c r="G18" s="14">
+        <v>2</v>
+      </c>
+      <c r="H18" s="14">
+        <v>160</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>975</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>465</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="166" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57E45770-7208-4ED9-A073-DDE4E51A6262}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -525,10 +525,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1626,26 +1622,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B19" s="14">
+        <v>480</v>
+      </c>
+      <c r="C19" s="14">
+        <v>60</v>
+      </c>
+      <c r="D19" s="14">
+        <v>130</v>
+      </c>
+      <c r="E19" s="14">
+        <v>40</v>
+      </c>
+      <c r="F19" s="14">
+        <v>350</v>
+      </c>
+      <c r="G19" s="14">
+        <v>7</v>
+      </c>
+      <c r="H19" s="14">
+        <v>220</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67F8BAF2-28A1-4E9E-96FD-503CF47F0CD8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>Bad Day.</t>
+  </si>
+  <si>
+    <t>learning something new.</t>
   </si>
 </sst>
 </file>
@@ -525,6 +528,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1668,26 +1675,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B20" s="14">
+        <v>480</v>
+      </c>
+      <c r="C20" s="14">
+        <v>60</v>
+      </c>
+      <c r="D20" s="14">
+        <v>140</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>200</v>
+      </c>
+      <c r="G20" s="14">
+        <v>4</v>
+      </c>
+      <c r="H20" s="14">
+        <v>210</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67F8BAF2-28A1-4E9E-96FD-503CF47F0CD8}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DAECD87-241A-4415-BFE6-55C976560EE2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>learning something new.</t>
+  </si>
+  <si>
+    <t>Prepration for CA.</t>
   </si>
 </sst>
 </file>
@@ -1721,26 +1724,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>0</v>
+      </c>
+      <c r="D21" s="14">
+        <v>110</v>
+      </c>
+      <c r="E21" s="14">
+        <v>20</v>
+      </c>
+      <c r="F21" s="14">
+        <v>350</v>
+      </c>
+      <c r="G21" s="14">
+        <v>7</v>
+      </c>
+      <c r="H21" s="14">
+        <v>120</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DAECD87-241A-4415-BFE6-55C976560EE2}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5E7CB05-9D99-4586-9574-BA96A51134BF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1770,26 +1770,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B22" s="14">
+        <v>360</v>
+      </c>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>30</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
+        <v>200</v>
+      </c>
+      <c r="G22" s="14">
+        <v>4</v>
+      </c>
+      <c r="H22" s="14">
+        <v>150</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>740</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>700</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5E7CB05-9D99-4586-9574-BA96A51134BF}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBAE38C0-B765-4341-A25B-E4887B15B440}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1816,26 +1816,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>60</v>
+      </c>
+      <c r="D23" s="14">
+        <v>60</v>
+      </c>
+      <c r="E23" s="14">
+        <v>40</v>
+      </c>
+      <c r="F23" s="14">
+        <v>350</v>
+      </c>
+      <c r="G23" s="14">
+        <v>7</v>
+      </c>
+      <c r="H23" s="14">
+        <v>120</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBAE38C0-B765-4341-A25B-E4887B15B440}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{633413F6-FC8E-42A8-9547-69DEB7B0F4A4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>Prepration for CA.</t>
+  </si>
+  <si>
+    <t>CA Prepration.</t>
   </si>
 </sst>
 </file>
@@ -1862,26 +1865,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B24" s="14">
+        <v>420</v>
+      </c>
+      <c r="C24" s="14">
+        <v>60</v>
+      </c>
+      <c r="D24" s="14">
+        <v>45</v>
+      </c>
+      <c r="E24" s="14">
+        <v>20</v>
+      </c>
+      <c r="F24" s="14">
+        <v>200</v>
+      </c>
+      <c r="G24" s="14">
+        <v>4</v>
+      </c>
+      <c r="H24" s="14">
+        <v>180</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>925</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>515</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{633413F6-FC8E-42A8-9547-69DEB7B0F4A4}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE54C12B-8491-4F91-AD69-09AC78404C93}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1911,26 +1911,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14">
+        <v>40</v>
+      </c>
+      <c r="E25" s="14">
+        <v>0</v>
+      </c>
+      <c r="F25" s="14">
+        <v>150</v>
+      </c>
+      <c r="G25" s="14">
+        <v>3</v>
+      </c>
+      <c r="H25" s="14">
+        <v>300</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="13"/>

--- a/12627834.xlsx
+++ b/12627834.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4929e24890d5afa0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE54C12B-8491-4F91-AD69-09AC78404C93}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{25496F8F-0EC5-4B52-9379-4310F8331873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9AE01EE-127E-42BF-A519-B6F361F4AAE1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1957,26 +1957,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B26" s="14">
+        <v>360</v>
+      </c>
+      <c r="C26" s="14">
+        <v>60</v>
+      </c>
+      <c r="D26" s="14">
+        <v>40</v>
+      </c>
+      <c r="E26" s="14">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14">
+        <v>360</v>
+      </c>
+      <c r="G26" s="14">
+        <v>6</v>
+      </c>
+      <c r="H26" s="14">
+        <v>120</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="13"/>
